--- a/benchmark/generated_files/CC-2_V_030.xlsx
+++ b/benchmark/generated_files/CC-2_V_030.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A2:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -442,17 +442,10 @@
     <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filiale: SEDE CENTRALE</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tipo conto: Conto corrente</t>
+          <t>Banca: Banca Sella</t>
         </is>
       </c>
     </row>
@@ -487,15 +480,15 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218945500 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:215802206 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2674.66</v>
+        <v>1639.97</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -509,11 +502,11 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212408395 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Pagam. POS - PAGAMENTO POS 18,66 EUR DEL 03.01.2026 A (ITA) BLUESPIRIT</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5302.3</v>
+        <v>-18.66</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -527,11 +520,11 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211961973 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:219894247 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4656.84</v>
+        <v>5021.84</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -541,15 +534,15 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212008786 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:214165129 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4023.48</v>
+        <v>2779.37</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -559,15 +552,15 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216859428 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:216198245 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3024.09</v>
+        <v>4395.97</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -577,15 +570,15 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212893896 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:216130336 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5231.35</v>
+        <v>1620.69</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -599,11 +592,11 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214266286 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:217862814 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>4840.9</v>
+        <v>4807.93</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -613,15 +606,15 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212599167 ORD. BETA CONSULTING SRL</t>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2261.34</v>
+        <v>-218.67</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -631,15 +624,15 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
+          <t>Bonif. v/fav. - RIF:216440403 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-65.09</v>
+        <v>4671.85</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -649,15 +642,15 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218357931 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:213190119 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>4646.53</v>
+        <v>4322.61</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -667,15 +660,15 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46035</v>
+        <v>46032</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213554947 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:216833399 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2322.09</v>
+        <v>5463.12</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -685,15 +678,15 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217607440 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:214214069 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4981.71</v>
+        <v>3317.37</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -703,15 +696,15 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212074040 ORD. DELTA SOLUTIONS SPA</t>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>5411.11</v>
+        <v>-288.21</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -725,11 +718,11 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219435884 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:212630201 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4654.04</v>
+        <v>4443.53</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -743,11 +736,11 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216370776 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:211229411 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4931.72</v>
+        <v>4305.1</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -757,15 +750,15 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213253897 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:215585660 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3502.93</v>
+        <v>5403.99</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -775,15 +768,15 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46043</v>
+        <v>46039</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Bonif. v/fav. - RIF:215691073 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-97.25</v>
+        <v>1991.06</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -793,15 +786,15 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46043</v>
+        <v>46040</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210643934 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:214272706 ORD. REGIONE LOMBARDIA BONUS</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4584.86</v>
+        <v>452.01</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -811,15 +804,15 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46043</v>
+        <v>46040</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211836929 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:218898646 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1917.96</v>
+        <v>4861.6</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -829,15 +822,15 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219763239 ORD. ROSSI MARCO GIROCONTO</t>
+          <t>Bonif. v/fav. - RIF:213813029 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-891.05</v>
+        <v>3605.33</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -847,15 +840,15 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46044</v>
+        <v>46041</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211758064 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:218813729 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1647.57</v>
+        <v>3146.04</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -865,15 +858,15 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46044</v>
+        <v>46041</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217151482 ORD. EPSILON DIGITAL SRL</t>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1919.06</v>
+        <v>-219.74</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -883,15 +876,15 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46045</v>
+        <v>46043</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214583958 ORD. EPSILON DIGITAL SRL</t>
+          <t>Disposizione - RIF:212115786 BEN. OFFICINA MECCANICA BRAMBILLA</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2346.88</v>
+        <v>-60.62</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -901,15 +894,15 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46045</v>
+        <v>46043</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217405045 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:215239391 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2376.14</v>
+        <v>4920.96</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
@@ -919,15 +912,15 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217050441 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:217962835 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4599.6</v>
+        <v>1802.23</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -937,15 +930,15 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46048</v>
+        <v>46046</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213510420 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:214216037 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>4096.54</v>
+        <v>4758.97</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -959,11 +952,11 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212642737 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:211553735 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>3111.26</v>
+        <v>3626.41</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -973,15 +966,15 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0075849 A CC 0123456</t>
+          <t>Bonif. v/fav. - RIF:219633330 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-796.37</v>
+        <v>4485.17</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -991,15 +984,15 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
+          <t>Bonif. v/fav. - RIF:213290759 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-62.4</v>
+        <v>3947.65</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1009,15 +1002,15 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46051</v>
+        <v>46050</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211791089 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:216951103 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>2226.69</v>
+        <v>359.75</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1031,11 +1024,11 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212103430 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:214976332 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2489.83</v>
+        <v>4929.03</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1045,15 +1038,15 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46054</v>
+        <v>46051</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211941228 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:211789302 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>4798.54</v>
+        <v>4197.81</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1067,11 +1060,11 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216766020 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:213311146 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2886.31</v>
+        <v>3192.44</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1081,15 +1074,15 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214795036 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:213541364 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>4459.43</v>
+        <v>4902.48</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1103,11 +1096,11 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218817964 ORD. EPSILON DIGITAL SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 46,13 EUR DEL 02.02.2026 A (ITA) CENTRO MEDICO SANTAGOSTINO</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4054.45</v>
+        <v>-46.13</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -1117,15 +1110,15 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46057</v>
+        <v>46055</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217508711 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:210269759 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>5147.78</v>
+        <v>1667.2</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1135,15 +1128,15 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46057</v>
+        <v>46055</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214128371 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:211684884 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>5136.35</v>
+        <v>3779.24</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1153,15 +1146,15 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46058</v>
+        <v>46055</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210387616 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
+          <t>Bonif. v/fav. - RIF:216614931 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>314.22</v>
+        <v>2501.29</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -1171,15 +1164,15 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46058</v>
+        <v>46056</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213350503 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:219090564 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>4222.35</v>
+        <v>4906.71</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1189,15 +1182,15 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
+          <t>Bonif. v/fav. - RIF:214131532 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>-240.7</v>
+        <v>2589.88</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -1207,15 +1200,15 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218903582 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:212958594 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1641.36</v>
+        <v>3456.75</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -1225,15 +1218,15 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216073818 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:211255802 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>4168.05</v>
+        <v>4633.69</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -1243,15 +1236,15 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213085925 ORD. ROSSI MARCO GIROCONTO</t>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>-749.8</v>
+        <v>-252.52</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -1261,15 +1254,15 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215570598 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:216485646 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>4658.53</v>
+        <v>2684.8</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -1279,15 +1272,15 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46062</v>
+        <v>46060</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212074018 ORD. EPSILON DIGITAL SRL</t>
+          <t>Bonif. v/fav. - RIF:213957974 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2842.97</v>
+        <v>3861.2</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -1297,15 +1290,15 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219649883 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>Bonif. v/fav. - RIF:216041197 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>367.87</v>
+        <v>2018.69</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -1315,15 +1308,15 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46065</v>
+        <v>46062</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218065626 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:218293469 ORD. ROSSI MARCO GIROCONTO</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>3155.05</v>
+        <v>-622.4400000000001</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -1337,11 +1330,11 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216733998 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:214139080 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2235.91</v>
+        <v>2354.19</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -1351,15 +1344,15 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212031137 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:214526016 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>3167.58</v>
+        <v>3540.23</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -1369,15 +1362,15 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216152608 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:215334546 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>4788.55</v>
+        <v>3684.65</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
@@ -1391,11 +1384,11 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210706189 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>GIROCONTO DA CC 0075849 A CC 0123456</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>2601.97</v>
+        <v>-380.34</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -1405,15 +1398,15 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217552842 ORD. CLIENTE ALFA S.P.A.</t>
+          <t>Bonif. v/fav. - RIF:213188178 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>4608.15</v>
+        <v>4325.77</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
@@ -1423,15 +1416,15 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213736199 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:216319220 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>3794.02</v>
+        <v>1949.22</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -1441,15 +1434,15 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 21,04 EUR DEL 18.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Bonif. v/fav. - RIF:210868054 ORD. DELTA SOLUTIONS SPA</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>-21.04</v>
+        <v>2528.03</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -1459,15 +1452,15 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210050421 ORD. GAMMA TECHNOLOGIES SRL</t>
+          <t>Bonif. v/fav. - RIF:210297760 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>4663.01</v>
+        <v>5213.25</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -1481,11 +1474,11 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218831440 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:213160647 ORD. GAMMA TECHNOLOGIES SRL</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3390.52</v>
+        <v>3983.49</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -1495,15 +1488,15 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214136095 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:214317890 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3690.32</v>
+        <v>2239.13</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -1513,15 +1506,15 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46075</v>
+        <v>46079</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215596864 ORD. DELTA SOLUTIONS SPA</t>
+          <t>Bonif. v/fav. - RIF:218645742 ORD. BETA CONSULTING SRL</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>5224.94</v>
+        <v>1977.54</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -1531,15 +1524,15 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46075</v>
+        <v>46079</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213486670 ORD. BETA CONSULTING SRL</t>
+          <t>Bonif. v/fav. - RIF:214875662 ORD. CLIENTE ALFA S.P.A.</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>5278.63</v>
+        <v>2048.39</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -1549,15 +1542,15 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Bonif. v/fav. - RIF:216182508 ORD. EPSILON DIGITAL SRL</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>-57.54</v>
+        <v>3851.39</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -1568,7 +1561,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Saldo finale: 20.734,16 EUR</t>
+          <t>Saldo finale: 1.389,67 EUR</t>
         </is>
       </c>
     </row>
